--- a/data/trans_bre/P3A_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -612,42 +612,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>57,87</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>44,56</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>39,17</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>30,6</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>223,09%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>112,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,35%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>53,48; 62,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>39,67; 49,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>34,68; 43,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>25,95; 34,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>185,26; 271,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>91,69; 136,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>67,51; 99,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>38,75; 59,42</t>
         </is>
       </c>
     </row>
@@ -712,42 +712,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>54,56</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>40,23</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>37,84</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>40,25</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>173,72%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,56%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>50,93; 58,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>36,34; 44,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>33,65; 41,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>25,67; 64,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>147,72; 204,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>81,18; 112,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>62,38; 86,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>38,6; 226,02</t>
         </is>
       </c>
     </row>
@@ -812,42 +812,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>47,56</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>41,93</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>36,13</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>25,44</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>120,39%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,53%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>42,77; 52,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,41; 46,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>31,83; 40,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>20,42; 32,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>98,79; 146,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>80,27; 117,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>57,89; 84,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>28,89; 50,09</t>
         </is>
       </c>
     </row>
@@ -912,42 +912,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>41,21</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>34,44</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>25,5</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>20,9</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>104,78%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,2; 45,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>29,96; 38,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>21,32; 29,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,68; 24,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>87,57; 124,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>58,5; 85,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>33,94; 51,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>23,8; 38,28</t>
         </is>
       </c>
     </row>
@@ -1012,42 +1012,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>49,87</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>39,87</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>34,27</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>30,24</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>145,82%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,32%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>47,7; 51,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,72; 42,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>32,35; 36,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,81; 42,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>133,71; 159,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>83,41; 99,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>59,17; 70,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,32; 88,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P3A_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30,6</t>
+          <t>30,76</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>49,13%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>53,48; 62,12</t>
+          <t>52,96; 62,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39,67; 49,25</t>
+          <t>39,6; 49,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34,68; 43,92</t>
+          <t>34,4; 43,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25,95; 34,99</t>
+          <t>26,61; 35,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>185,26; 271,01</t>
+          <t>181,24; 270,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,69; 136,22</t>
+          <t>91,09; 134,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,51; 99,53</t>
+          <t>66,28; 97,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>38,75; 59,42</t>
+          <t>40,38; 62,16</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40,25</t>
+          <t>26,92</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>41,42%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>50,93; 58,51</t>
+          <t>50,89; 58,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,34; 44,13</t>
+          <t>36,03; 44,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,65; 41,59</t>
+          <t>33,88; 41,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,67; 64,95</t>
+          <t>23,28; 31,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>147,72; 204,22</t>
+          <t>148,34; 208,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,18; 112,14</t>
+          <t>80,29; 113,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,38; 86,51</t>
+          <t>62,3; 85,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>38,6; 226,02</t>
+          <t>34,39; 50,42</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25,44</t>
+          <t>23,1</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>34,17%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>42,77; 52,39</t>
+          <t>42,95; 51,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37,41; 46,69</t>
+          <t>37,42; 46,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,83; 40,73</t>
+          <t>31,87; 40,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20,42; 32,09</t>
+          <t>18,53; 27,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>98,79; 146,2</t>
+          <t>98,9; 143,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>80,27; 117,42</t>
+          <t>80,04; 118,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,89; 84,04</t>
+          <t>57,49; 83,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28,89; 50,09</t>
+          <t>26,17; 43,15</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20,9</t>
+          <t>21,29</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>32,13%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>37,2; 45,36</t>
+          <t>37,14; 45,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,96; 38,43</t>
+          <t>30,29; 38,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,32; 29,45</t>
+          <t>21,23; 29,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,68; 24,83</t>
+          <t>17,74; 25,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,57; 124,14</t>
+          <t>89,18; 123,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,5; 85,0</t>
+          <t>58,32; 84,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,94; 51,43</t>
+          <t>33,78; 51,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,8; 38,28</t>
+          <t>25,74; 40,1</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30,24</t>
+          <t>25,16</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>38,42%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>47,7; 51,97</t>
+          <t>47,68; 52,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>37,72; 42,01</t>
+          <t>37,79; 42,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32,35; 36,43</t>
+          <t>32,19; 36,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,81; 42,85</t>
+          <t>22,8; 27,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>133,71; 159,42</t>
+          <t>132,88; 159,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>83,41; 99,05</t>
+          <t>83,6; 100,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,17; 70,77</t>
+          <t>58,67; 70,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>37,32; 88,84</t>
+          <t>33,81; 42,74</t>
         </is>
       </c>
     </row>
